--- a/SuppXLS/Scen_UC_BIO_CEMENTHEAT_5_15.xlsx
+++ b/SuppXLS/Scen_UC_BIO_CEMENTHEAT_5_15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE2E509-4F7C-4BD2-B91B-22F9ACC7D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39248E9-DA8A-43E1-B4F6-EEABB517F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="36300" yWindow="3675" windowWidth="17280" windowHeight="8880" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
     <sheet name="BIO_CEMENTHEAT_5_15" sheetId="1" r:id="rId1"/>
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>-0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="M6">
         <v>0</v>
